--- a/KRİTİK PARÇA LİSTESİ/Kritik-Parca-Listeleri.xlsx
+++ b/KRİTİK PARÇA LİSTESİ/Kritik-Parca-Listeleri.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,11 @@
           <t>TERMİK RÖLESİ LR2K0305 0,54-0,8A</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>photos/10 00243.jpg</t>
+        </is>
+      </c>
       <c r="D513" t="inlineStr">
         <is>
           <t>Rezistans komple / pano</t>
@@ -3762,7 +3766,11 @@
           <t>TERMİK RÖLESİ LR2K0306 0,80-1,2A</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr"/>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>photos/10 00244.jpg</t>
+        </is>
+      </c>
       <c r="D514" t="inlineStr">
         <is>
           <t>Rezistans komple / pano</t>
@@ -4002,7 +4010,11 @@
           <t>TERMİK RÖLESİ LR2K0314 5,80-8,0A</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>photos/10 00249.jpg</t>
+        </is>
+      </c>
       <c r="D519" t="inlineStr">
         <is>
           <t>Rezistans komple / pano</t>
@@ -4098,7 +4110,11 @@
           <t>FAZ KORUMA RÖLESİ MKS-03</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>photos/10 00258.jpg</t>
+        </is>
+      </c>
       <c r="D521" t="inlineStr">
         <is>
           <t>Pano</t>

--- a/KRİTİK PARÇA LİSTESİ/Kritik-Parca-Listeleri.xlsx
+++ b/KRİTİK PARÇA LİSTESİ/Kritik-Parca-Listeleri.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -576,24 +576,84 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stok ipucu</t>
+          <t>Stok C+1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C+3 → genelde stok 0, listede kalsın | 1+K → depo stoku adayı</t>
+          <t>3 adet — sık aşınma, kritik — depo seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stok A/B+1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2 adet — sık aşınma — depo seti</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Stok 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1 adet — orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stok C+3+K/O</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1 adet — kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stok C+3+Z</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0 adet — kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Stok A/B+3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0 adet — seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Güncelleme</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -608,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J525"/>
+  <dimension ref="A1:K534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -619,8 +679,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,10 +727,15 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>Stok gerekçesi</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Not</t>
         </is>
@@ -3186,7 +3252,11 @@
           <t>AMORTİSÖR 175N</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>photos/10 12433.jpg</t>
+        </is>
+      </c>
       <c r="D502" t="inlineStr">
         <is>
           <t>LYM 950</t>
@@ -3214,10 +3284,15 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>C+3+Z — liste; imalat/termin</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
         <is>
           <t>LYM 950 kapak/kaldırma; arızada açılış veya emniyet kilidi etkilenir. Stokta tutulmaz, sipariş kodu dokümante.</t>
         </is>
@@ -3234,7 +3309,11 @@
           <t>AMORTİSÖR 350N</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>photos/10 12433.jpg</t>
+        </is>
+      </c>
       <c r="D503" t="inlineStr">
         <is>
           <t>LYM 1150</t>
@@ -3262,10 +3341,15 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>C+3+Z — liste; imalat/termin</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
         <is>
           <t>LYM 1150 için 350N kapasite; normal ömürde aşınma beklenmez, hasar/yaşlanma durumunda değişim.</t>
         </is>
@@ -3282,7 +3366,11 @@
           <t>AMORTİSÖR 1000N</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>photos/10 12433.jpg</t>
+        </is>
+      </c>
       <c r="D504" t="inlineStr">
         <is>
           <t>LYM 1350</t>
@@ -3310,12 +3398,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>C+3+Z — liste; imalat/termin</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>LYM 1350 ağır kapak; tek kaynak imalat — listede mutlaka, depo 0.</t>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>LYM 1350 ağır kapak; tek kaynak imalat — listede mutlaka, depoda tutulmaz.</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3423,11 @@
           <t>AMORTİSÖR 1400N</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr"/>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>photos/10 12433.jpg</t>
+        </is>
+      </c>
       <c r="D505" t="inlineStr">
         <is>
           <t>LYM 1500</t>
@@ -3358,10 +3455,15 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>C+3+Z — liste; imalat/termin</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
         <is>
           <t>LYM 1500 en yüksek kapasite amortisör; arızada kapak operasyonu durur.</t>
         </is>
@@ -3378,7 +3480,11 @@
           <t>SWITCH L5K13MEP123 1NO 1NC</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>photos/10 03262.jpg</t>
+        </is>
+      </c>
       <c r="D506" t="inlineStr">
         <is>
           <t>LYM 1350, LYM 1500</t>
@@ -3401,15 +3507,20 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>C+3+K — emniyet devresi; ucuz yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
+        <is>
+          <t>C+3+K → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
         <is>
           <t>Kapak/kilitleme emniyet devresi (1NO 1NC); arızada makine çalışmaz veya kilit onayı alınmaz.</t>
         </is>
@@ -3426,7 +3537,11 @@
           <t>SWITCH L5K27MUM331 2NO 1NC</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>photos/10 00260.jpg</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr">
         <is>
           <t>LYM 1350, LYM 1500</t>
@@ -3449,17 +3564,22 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>C+3+K — emniyet devresi; ucuz yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>İkinci emniyet switch (2NO 1NC); L5K13 ile birlikte kapak zinciri — piyasa parçası, 2 adet depo önerilir.</t>
+          <t>C+3+K → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>İkinci emniyet switch (2NO 1NC); L5K13 ile birlikte kapak zinciri — piyasa parçası.</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3594,11 @@
           <t>REZİSTANS KOMPLESİ 8250W M TİPİ</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr"/>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>photos/07 00309.jpg</t>
+        </is>
+      </c>
       <c r="D508" t="inlineStr">
         <is>
           <t>LYM 950–1500</t>
@@ -3487,27 +3611,32 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>A+2+Z — komple uzun termin; 1 yedek makine başına değil, hat bazlı</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>Komple sipariş veya alt parça (termik, kontaktör) ayrı; kurutma ısıtması — komple stok termin riski için minimum 1.</t>
+          <t>A+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Komple sipariş veya alt parça (termik, kontaktör) ayrı; kurutma ısıtması — rezistans sık yanar, komple termini uzun.</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3679,17 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>C+3+O — emniyet; 1 adet merkezi depo</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>Tank/kazan seviye emniyeti; arızada dolum veya emniyet stop. Paslanmaz gövde — sipariş terminine göre 1 yedek.</t>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Tank/kazan seviye emniyeti; arızada dolum veya emniyet stop. Paslanmaz gövde, sipariş termini var.</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3704,11 @@
           <t>DÜZ FİŞ BEMİS 5*32A ENVERSÖR (BEM45-084)</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr"/>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>photos/10 00307.jpg</t>
+        </is>
+      </c>
       <c r="D510" t="inlineStr">
         <is>
           <t>LYM 950–1350</t>
@@ -3593,15 +3731,20 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>B+3+K — güç bağlantısı; 1 yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
+        <is>
+          <t>B+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
         <is>
           <t>Kurutma hattı 32A enversör düz fiş; mekanik hasar/yanık olay bazlı — Bemis kodu ile hızlı tedarik.</t>
         </is>
@@ -3618,7 +3761,11 @@
           <t>DUVAR PRİZİ BEMİS 5*32A 90 DERECE (BEM45-103)</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr"/>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>photos/10 00308.jpg</t>
+        </is>
+      </c>
       <c r="D511" t="inlineStr">
         <is>
           <t>LYM 950–1350</t>
@@ -3641,15 +3788,20 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>B+3+K — 00307 ile çift; 1 yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
+        <is>
+          <t>B+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
         <is>
           <t>90° duvar prizi; 10 00307 ile set — arızada kurutma devresi beslemesi kesilebilir.</t>
         </is>
@@ -3666,7 +3818,11 @@
           <t>TERMOKUPL ETB30F06-2Ç</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr"/>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>photos/10 01343.jpg</t>
+        </is>
+      </c>
       <c r="D512" t="inlineStr">
         <is>
           <t>LYM 950–1500</t>
@@ -3689,17 +3845,22 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>C+3+O — sıcaklık regülasyonu; 2 adet</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>Sıcaklık ölçümü; arızada kontrol/koruma devre dışı. ETB30F06-2Ç — bayi termin, 2 adet önerilir.</t>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Sıcaklık ölçümü; arızada kontrol/koruma devre dışı. ETB30F06-2Ç — bayi termini var.</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3877,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>photos/10 00243.jpg</t>
+          <t>photos/10 00249.jpg</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -3741,15 +3902,20 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
         <is>
           <t>Schneider LR2K0305; düşük akım motor/koruma hattı — rezistans komple BOM’da olabilir.</t>
         </is>
@@ -3768,7 +3934,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>photos/10 00244.jpg</t>
+          <t>photos/10 00249.jpg</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -3793,15 +3959,20 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
         <is>
           <t>LR2K0306 0,80–1,2 A; termik setin parçası — kontaktör üzerine takılı kullanım.</t>
         </is>
@@ -3818,7 +3989,11 @@
           <t>TERMİK RÖLESİ LR2K0307 1,20-1,8A</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>photos/10 00249.jpg</t>
+        </is>
+      </c>
       <c r="D515" t="inlineStr">
         <is>
           <t>Rezistans komple / pano</t>
@@ -3841,15 +4016,20 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
         <is>
           <t>LR2K0307 1,2–1,8 A; aşırı akımda açma — periyodik kontrol önerilir.</t>
         </is>
@@ -3866,7 +4046,11 @@
           <t>TERMİK RÖLESİ LR2K0308 1,80-2,6A</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr"/>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>photos/10 00249.jpg</t>
+        </is>
+      </c>
       <c r="D516" t="inlineStr">
         <is>
           <t>Rezistans komple / pano</t>
@@ -3889,15 +4073,20 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
         <is>
           <t>LR2K0308 1,8–2,6 A; yanlış akım aralığı seçimi trip veya koruma kaybına yol açar.</t>
         </is>
@@ -3914,7 +4103,11 @@
           <t>TERMİK RÖLESİ LR2K0310 2,60-3,7A</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr"/>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>photos/10 00249.jpg</t>
+        </is>
+      </c>
       <c r="D517" t="inlineStr">
         <is>
           <t>LYM 950 / pano</t>
@@ -3937,17 +4130,22 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>LYM 950 panoda montajlı (2,6–3,7 A); sınıflandırma diğer LR2K ile aynı — stok bandı başına 2.</t>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>LYM 950 panoda montajlı (2,6–3,7 A); sınıflandırma diğer LR2K ile aynı — her akım bandı ayrı stoklanır.</t>
         </is>
       </c>
     </row>
@@ -3962,7 +4160,11 @@
           <t>TERMİK RÖLESİ LR2K0312 3,70-5,5A</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr"/>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>photos/10 00249.jpg</t>
+        </is>
+      </c>
       <c r="D518" t="inlineStr">
         <is>
           <t>LYM 950 / pano</t>
@@ -3985,15 +4187,20 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
         <is>
           <t>LYM 950 pano hattı (3,7–5,5 A); 10 00247 ile aynı stok kuralı.</t>
         </is>
@@ -4037,15 +4244,20 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
         <is>
           <t>LR2K0314 orta-yüksek akım; rezistans/kompressör hatları için set stoğu.</t>
         </is>
@@ -4062,7 +4274,11 @@
           <t>TERMİK RÖLESİ LR2K0321 10,0-14A</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr"/>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>photos/10 00249.jpg</t>
+        </is>
+      </c>
       <c r="D520" t="inlineStr">
         <is>
           <t>Rezistans komple / pano</t>
@@ -4085,15 +4301,20 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>A+2+K — ucuz; akım bandı başına min. 2 (LR2K set)</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
+        <is>
+          <t>A+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
         <is>
           <t>LR2K0321 10–14 A; en yüksek akım bandı sette — depoda mutlaka bulunsun.</t>
         </is>
@@ -4127,7 +4348,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -4137,17 +4358,22 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>A+2+K — faz kaybı koruması; 1 yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>380 V faz sırası/kaybı; arızada pompa/fan koruma trip — piyasa MKS-03, 1 adet yeterli.</t>
+          <t>A+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>380 V faz sırası/kaybı; arızada pompa/fan koruma trip — piyasa parçası MKS-03.</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4388,11 @@
           <t>TERMOSTAT DİJİTAL LT 102J GEMO</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr"/>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>photos/10 00236.jpg</t>
+        </is>
+      </c>
       <c r="D522" t="inlineStr">
         <is>
           <t>Pano</t>
@@ -4175,7 +4405,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -4185,17 +4415,22 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>A+2+K — ikincil sıcaklık limiti; 1 yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>Gemo LT 102J; limit termostat — DT 481’den farklı görev, yedek 1 adet.</t>
+          <t>A+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Gemo LT 102J; limit termostat — DT 481’den farklı görev.</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4445,11 @@
           <t>TERMOSTAT DİJİTAL DT 481 GEMO</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr"/>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>photos/10 00237.jpg</t>
+        </is>
+      </c>
       <c r="D523" t="inlineStr">
         <is>
           <t>Pano</t>
@@ -4233,15 +4472,20 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>B+3+K — ana regülasyon; 1 yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
+        <is>
+          <t>B+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
         <is>
           <t>Gemo DT 481; proses sıcaklık regülasyonu — arızada kurutma kalitesi/duruş riski B sınıfı.</t>
         </is>
@@ -4258,7 +4502,11 @@
           <t>NOZZLE 1/4" 0 DERECE AÇILI  PASLANMAZ  (ÇNK)</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>photos/07 00253.jpg</t>
+        </is>
+      </c>
       <c r="D524" t="inlineStr">
         <is>
           <t>LYM 950–1500</t>
@@ -4271,23 +4519,32 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G524" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>A+2 — Ulaş. atanmadı; nozzle set (geçici 2)</t>
+          <t>set</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>ÇNK paslanmaz 0° püskürtme; tıkanma/aşınmada basınç dağılımı bozulur — makine durmaz (A), kalite düşer. Ulaşılabilirlik (K/O/Z) henüz girilmedi.</t>
+          <t>A+1+Z → 1 set · makinedeki nozzle takımı kadar — 1 set</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>ÇNK paslanmaz 0° püskürtme; tıkanma/aşınmada basınç dağılımı bozulur — makine durmaz (A), kalite düşer. Kendi imalat (Z).</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4559,11 @@
           <t>NOZZLE 650.724.1C.CC</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>photos/07 00253.jpg</t>
+        </is>
+      </c>
       <c r="D525" t="inlineStr">
         <is>
           <t>LYM 950–1500</t>
@@ -4315,23 +4576,545 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>A+1+O → 1 set · makinedeki nozzle takımı kadar — 1 set</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Lechler 650 serisi yassı huzme nozzle (650.724.1C.CC); 07 00253 ile aynı görev, bayi üzerinden tedarik (O).</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>10 01332</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K1610M7 220V</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr"/>
-      <c r="H525" t="inlineStr">
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K1610M7, 16 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>10 01331</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K0910M7 220V</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>A+2 — Ulaş. atanmadı; nozzle set (geçici 2)</t>
-        </is>
-      </c>
-      <c r="J525" t="inlineStr">
-        <is>
-          <t>Tedarikçi tip nozzle (650.724.1C.CC); 07 00253 ile aynı A/2 sınıfı — ulaşılabilirlik atanınca stok satırı güncellenir.</t>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K0910M7, 9 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>10 02314</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K0610M7 220V</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K0610M7, 6 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>10 02818</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>POMPA ATLANTİS KAF 300T/304 3HP 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>photos/10 02818.jpg</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>LYM 950–1500</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>10 06316</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS GCEA 370/3 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>photos/10 06316.jpg</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>LYM 950–1500</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>10 08525</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS GCEA 370/2 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>photos/10 08525.jpg</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>LYM 950</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>10 17117</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>POMPA ATLANTİS KAF 150 T</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>photos/10 17117.jpg</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>LYM 950</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>10 17118</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>POMPA WATER SOUND 1019 BB300/150 2HP 380V 50HZ</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>photos/10 17118.jpg</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>LYM 950</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>10 17119</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>POMPA WATER SOUND 1020 BB500/220 3HP 380V 50HZ</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>photos/10 17119.jpg</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>LYM 950–1500</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +5129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J503"/>
+  <dimension ref="A1:K534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4357,8 +5140,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4404,10 +5188,15 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>Stok gerekçesi</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Not</t>
         </is>
@@ -6924,10 +7713,14 @@
           <t>REZİSTANS KOMPLESİ 8250W M TİPİ</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>photos/07 00309.jpg</t>
+        </is>
+      </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>VDL 2B ailesi</t>
+          <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -6937,27 +7730,32 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>A+2+Z — VDL komple; imalat termin</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>VDL 2B kurutma rezistans komplesi; LYM ile aynı kod — VDL adetleri daha yüksek, komple 1 yedek önerilir.</t>
+          <t>A+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>VDL 2B kurutma rezistans komplesi; LYM ile aynı kod — VDL'de makine başına adet daha yüksek.</t>
         </is>
       </c>
     </row>
@@ -6972,10 +7770,14 @@
           <t>TERMOKUPL ETB30F06-2Ç</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>photos/10 01343.jpg</t>
+        </is>
+      </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>VDL 40–60 2B</t>
+          <t>VDL 2B 40/50/60</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -6995,17 +7797,1741 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>VDL 40/50/60 2B modellerde sıcaklık geri beslemesi; kırılma/okuma hatasında C etkisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>10 02634</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>TERMOKUPUL ETB30F06-4Ç</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>photos/10 01343.jpg</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>ETB30F06 ailesi, farklı kablo boyu. Arızada sıcaklık kontrolü devre dışı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>10 02976</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>TERMOKUPUL ETB30F06-5Ç</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>photos/10 01343.jpg</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>VDL 2B 60</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>ETB30F06 ailesi, farklı kablo boyu. Arızada sıcaklık kontrolü devre dışı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>07 16791</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>SEVİYE SENSÖRÜ ÇAT.TİP VEGASWING 51 DİŞ ÇEKİLMİŞ</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>photos/07 16791.jpg</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>VEGASWING 51 çatal tip seviye sensörü; rezistansı kuru çalışmaya karşı korur, arızada makine durur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>10 07455</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>REZİSTANS 220V 2000W 112CM SERP. DİKİŞSİZ AISI316</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr">
-        <is>
-          <t>C+3+O — VDL sıcaklık; 2 adet</t>
-        </is>
-      </c>
-      <c r="J503" t="inlineStr">
-        <is>
-          <t>VDL 40/50/60 2B modellerde sıcaklık geri beslemesi; kırılma/okuma hatasında C etkisi.</t>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>A+1+O → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>2B tank ısıtıcısı (2000 W, AISI316). Bir eleman yanarsa ısınma süresi uzar, proses sıcaklığı tutmayabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>10 17118</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>POMPA WATER SOUND 1019 BB300/150 2HP 380V 50HZ</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>photos/10 17118.jpg</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40/50/80</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>10 02818</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>POMPA ATLANTİS KAF 300T/304 3HP 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>photos/10 02818.jpg</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>VDL 2B 60/80</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>10 06316</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS GCEA 370/3 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>photos/10 06316.jpg</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>VDL 2B 60/80</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>10 06364</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS GCEA 370/1 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>photos/10 06364.jpg</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>10 08525</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS GCEA 370/2 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>photos/10 08525.jpg</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>VDL 2B 50</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>10 17117</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>POMPA ATLANTİS KAF 150 T</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>photos/10 17117.jpg</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>10 17119</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>POMPA WATER SOUND 1020 BB500/220 3HP 380V 50HZ</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>photos/10 17119.jpg</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>VDL 2B 60</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>10 17125</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>POMPA ATLANTİS KAF 200T/304 3HP 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>photos/10 17125.jpg</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>VDL 1B 40</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>07 10970</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ VDL 40 2500 1B</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>VDL 1B 40</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Tambur/sepet tahriki; arızada makine çalışmaz. Modele özel komple — motor ve redüktör alt kodları ile ortak stok değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>07 08589</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ VDL 40 3500 2B</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>VDL 2B 40</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Tambur/sepet tahriki; arızada makine çalışmaz. Modele özel komple — motor ve redüktör alt kodları ile ortak stok değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>07 09267</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ VDL 50 4250 2B</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>VDL 2B 50</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Tambur/sepet tahriki; arızada makine çalışmaz. Modele özel komple — motor ve redüktör alt kodları ile ortak stok değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>07 08941</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ VDL 60 5500 2B</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>VDL 2B 60</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Tambur/sepet tahriki; arızada makine çalışmaz. Modele özel komple — motor ve redüktör alt kodları ile ortak stok değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>07 11744</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ VDL 80 6500 2B</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>VDL 2B 80</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Tambur/sepet tahriki; arızada makine çalışmaz. Modele özel komple — motor ve redüktör alt kodları ile ortak stok değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>07 00670</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>EMİŞ FİLTRESİ KOMPLESİ (PYM2,KBN,VDL,ULT,KNV)</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>B+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Pompa emiş filtresi; tıkanmada pompa kavitasyonu ve debi kaybı. Elek periyodik temizlenir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>07 10214</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>ÖN FİLTRE NS KOMPLESİ</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>photos/07 10214.jpg</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>B+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Ön filtre komplesi (makinede 8 adede kadar); tıkanma/yırtılmada yıkama kalitesi düşer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>07 04649</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>YAĞ SIYIRICI KOMPLESİ TİP 3 MONTAJ</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Yağ sıyırıcı komple; arızada makine çalışır, banyo ömrü kısalır. Alt parçalar (motor, kontaktör, termik) ayrı stoklanır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>07 05243</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>OTOMATİK TANK BOŞALTMA (VDL 40-50 2B)</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Otomatik tank boşaltma; arızada boşaltma manuel yapılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>07 10969</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>OTOMATİK TANK BOŞALTMA (VDL 40 1B)</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>VDL 1B 40</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Otomatik tank boşaltma; arızada boşaltma manuel yapılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>07 00512</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>VDL DOZAJ ÜNİTESİ</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>A+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Kimyasal dozaj; arızada manuel dozaj ile çalışılabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>07 00554</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>VDL SIZINTI TAVASI UYARI SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50/60/80</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>B+3+O → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Sızıntı tavası uyarı sistemi; arızada sızıntı fark edilmez, zemin/pano riski.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>10 02006</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>NOZZLE 632.804.16.CC</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>photos/07 00253.jpg</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>VDL 2B 60/80</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>A+1+O → 1 set · makinedeki nozzle takımı kadar — 1 set</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Lechler 632 serisi yassı huzme nozzle; makinede 66 adede kadar. Tıkanma/aşınmada yıkama basıncı ve kalitesi düşer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>10 01384</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>YAPRAK RÖLE APF30324-VDS-KK SOKET 1C/O 24VDC</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>photos/10 01384.jpg</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>B+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>24 VDC yaprak röle (soketli); arızada bağlı fonksiyon çalışmaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>10 00262</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>BUTON MANDAL B100S20</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>photos/10 00262.jpg</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>B+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Mandallı buton B100S20; acil stop olarak kullanılıyorsa önem C'dir — devre şemasından doğrulayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>10 02780</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>SİNYAL LAMBASI S222S SARI 22MM 220V.</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>photos/10 02780.jpg</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>VDL 2B 40/50</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>A+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Sinyal / tepe lambası; arızada makine çalışır, uyarı görülmez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>10 01332</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K1610M7 220V</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K1610M7, 16 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>10 01331</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K0910M7 220V</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K0910M7, 9 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>10 02314</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K0610M7 220V</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K0610M7, 6 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
         </is>
       </c>
     </row>
@@ -7020,7 +9546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J505"/>
+  <dimension ref="A1:K548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7031,8 +9557,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7078,10 +9605,15 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>Stok gerekçesi</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Not</t>
         </is>
@@ -9598,10 +12130,14 @@
           <t>REZİSTANS KOMPLESİ 8250W M TİPİ</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>photos/07 00309.jpg</t>
+        </is>
+      </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>KBN 1B ailesi</t>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -9611,27 +12147,32 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>A+2+Z — KBN komple; imalat termin</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>KBN 1B parça yıkama hattı 8250 W M tipi komple; alt termikler LYM listesinde ayrı.</t>
+          <t>A+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>KBN parça yıkama hattı 8250 W M tipi komple; alt termikler LYM listesinde ayrı.</t>
         </is>
       </c>
     </row>
@@ -9646,10 +12187,14 @@
           <t>TERMOKUPL ETB30F06-2Ç</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>photos/10 01343.jpg</t>
+        </is>
+      </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>KBN 1B</t>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1850</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -9669,17 +12214,22 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>C+3+O — KBN 1B; 2 adet</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>KBN 1B çok noktalı termokupl kullanımı; aynı kod LYM/VDL ile ortak stoklanabilir.</t>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>KBN'de çok noktalı termokupl kullanımı; aynı kod LYM/VDL ile ortak stoklanabilir.</t>
         </is>
       </c>
     </row>
@@ -9694,10 +12244,14 @@
           <t>SWITCH L5K13MEP123 1NO 1NC</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>photos/10 03262.jpg</t>
+        </is>
+      </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>KBN 1B</t>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -9717,17 +12271,22 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>C+3+K — KBN’de 7 adet montaj; merkezi 3 yedek</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>KBN 1B’de yüksek adetli emniyet switch; LYM ile aynı parça — ortak depo 3 adet önerilir.</t>
+          <t>C+3+K → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>KBN'de yüksek adetli emniyet switch; LYM ile aynı parça — ortak depodan karşılanabilir.</t>
         </is>
       </c>
     </row>
@@ -9742,10 +12301,14 @@
           <t>NOZZLE 1/4" 0 DERECE AÇILI  PASLANMAZ  (ÇNK)</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr"/>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>photos/07 00253.jpg</t>
+        </is>
+      </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>KBN 1B</t>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -9755,23 +12318,2387 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>A+1+Z → 1 set · makinedeki nozzle takımı kadar — 1 set</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>KBN yıkama hattı; LYM ile ortak kod — kendi imalat (Z).</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>07 15142</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>REZİSTANS KOMPLESİ 8000W 50CM DÜZ DİKİŞSİZ</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>KBN 2B 2050</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
-      <c r="H505" t="inlineStr">
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>A+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>KBN 2B 2050'de 8250 W M tipi yerine kullanılan 8000 W düz komple; imalat termini uzun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>07 16791</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>SEVİYE SENSÖRÜ ÇAT.TİP VEGASWING 51 DİŞ ÇEKİLMİŞ</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>photos/07 16791.jpg</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>VEGASWING 51 çatal tip seviye sensörü; rezistansı kuru çalışmaya karşı korur, arızada makine durur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>07 16782</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>KBN SEPET DURDURMA ÜST SENSÖR KOMPLESİ</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/2050</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Sepet durdurma üst sensör komplesi; arızada sepet konumlanamaz, çevrim başlamaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>10 00241</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>SENSÖR XUK1 ARCNL2</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>photos/10 00241.jpg</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Telemecanique XUK1 reflektörlü fotosel; sepet konum / el koruma sinyali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>10 00242</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>REFLEKTÖR XUZC50</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>photos/10 00242.jpg</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>A+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>XUK1 fotosel reflektörü; kırılma/kirlenmede sensör sinyal vermez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>07 04466</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>EL KORUMA FOTOSELLİ SENSÖR KOMPLESİ KBN 1B</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>El koruma emniyet komplesi; arızada emniyet onayı yok, makine çalışmaz. Sensör/bariyer alt parçası ayrıca listede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>07 07740</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>EL KORUMA FOTOSELLİ SENSÖR KOMPLESİ KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>El koruma emniyet komplesi; arızada emniyet onayı yok, makine çalışmaz. Sensör/bariyer alt parçası ayrıca listede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>07 04465</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>EL KORUMA LAZER IŞIN BARİYERİ KOMPLESİ KBN 1B</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>El koruma emniyet komplesi; arızada emniyet onayı yok, makine çalışmaz. Sensör/bariyer alt parçası ayrıca listede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>07 07741</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>EL KORUMA LAZER IŞIN BARİYERİ KOMPLESİ KBN 2B</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>C+3+Z → 0 adet · kritik, seyrek, imalat / uzun termin — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>El koruma emniyet komplesi; arızada emniyet onayı yok, makine çalışmaz. Sensör/bariyer alt parçası ayrıca listede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>10 16720</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>IŞIK BARİYERİ SF4D-H48 USF4DH48 PANASONIC 95CM</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>photos/10 16720.jpg</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>C+3+O → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Panasonic SF4D-H48 ışık bariyeri (95 cm); el koruma emniyeti — arızada makine çalışmaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>10 05035</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>SWITCH LK20K27 ANI HARK.1NK+2NA KONTAK BLOK</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>photos/10 05035.jpg</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>C+3+K → 1 adet · kritik ama seyrek — 1 emniyet yedeği</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Emas LK20K27 yedek kontak blok (1NK+2NA); sınır şalterinin kontak bloğu — kapak/konum emniyeti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>10 00694 12</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS ESHE 32-200/40 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>photos/10 00694 12.jpg</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I505" t="inlineStr">
-        <is>
-          <t>A+2 — Ulaş. atanmadı; nozzle set (geçici 2)</t>
-        </is>
-      </c>
-      <c r="J505" t="inlineStr">
-        <is>
-          <t>KBN 1B yıkama hattı; LYM ile ortak kod — ulaşılabilirlik henüz yok.</t>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>10 00694 10</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS ESHE 32-160/22 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>photos/10 00694 10.jpg</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650/1850</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>10 00694 11</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>POMPA GOULDS ESHE 32-200/30 380V/50HZ</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>photos/10 00694 11.jpg</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>KBN 1B 1850</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>10 17115</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>POMPA ATLANTİS CA 65-40/7,5T</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>photos/10 17115.jpg</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>10 17121</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>POMPA HMSE 40-200/75</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Yıkama/sirkülasyon pompası; arızada yıkama durur. Mekanik salmastra aşınır — salmastra setini ayrıca değerlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>07 08366</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ KBN 1650</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Sepet tahriki; arızada makine çalışmaz. YILMAZ ve SEW alternatif tedarikçi — sahadaki markaya göre stoklayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>07 08367</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP SEW KBN 1650</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Sepet tahriki; arızada makine çalışmaz. YILMAZ ve SEW alternatif tedarikçi — sahadaki markaya göre stoklayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>07 08380</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ KBN 1850</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>KBN 1B 1850 · KBN 2B 1850</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Sepet tahriki; arızada makine çalışmaz. YILMAZ ve SEW alternatif tedarikçi — sahadaki markaya göre stoklayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>07 08381</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP SEW KBN 1850</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>KBN 1B 1850 · KBN 2B 1850</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Sepet tahriki; arızada makine çalışmaz. YILMAZ ve SEW alternatif tedarikçi — sahadaki markaya göre stoklayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>07 08385</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP YILMAZ KBN 2050</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>KBN 1B 2050/2350 · KBN 2B 2050</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Sepet tahriki; arızada makine çalışmaz. YILMAZ ve SEW alternatif tedarikçi — sahadaki markaya göre stoklayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>07 08386</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>REDÜKTÖR VE MOTOR KOMP SEW KBN 2050</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>KBN 1B 2050/2350 · KBN 2B 2050</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>C+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Sepet tahriki; arızada makine çalışmaz. YILMAZ ve SEW alternatif tedarikçi — sahadaki markaya göre stoklayın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>07 00670</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>EMİŞ FİLTRESİ KOMPLESİ (PYM2,KBN,VDL,ULT,KNV)</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>B+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Pompa emiş filtresi; tıkanmada pompa kavitasyonu ve debi kaybı. Elek periyodik temizlenir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>07 10214</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>ÖN FİLTRE NS KOMPLESİ</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>photos/07 10214.jpg</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850 · KBN 2B 1650/2050</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>B+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Ön filtre komplesi (makinede 8 adede kadar); tıkanma/yırtılmada yıkama kalitesi düşer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>07 01221</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>ÖN FİLTRE KOMPLESİ</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>photos/07 10214.jpg</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>KBN 1B 2050/2350 · KBN 2B 1850</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>B+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Ön filtre komplesi (makinede 8 adede kadar); tıkanma/yırtılmada yıkama kalitesi düşer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>07 01248</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>SEPET TEKER DELRİNİ KBN ORTA DESTEK</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>B+1+Z → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Sepet orta destek teker delrini; aşınmada sepet sarsılır/sıkışır. Makinede 3 adet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>10 02006</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>NOZZLE 632.804.16.CC</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>photos/07 00253.jpg</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>A+1+O → 1 set · makinedeki nozzle takımı kadar — 1 set</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Lechler 632 serisi yassı huzme nozzle; makinede 66 adede kadar. Tıkanma/aşınmada yıkama basıncı ve kalitesi düşer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>07 05764</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>YAĞ SIYIRICI KOMPLESİ TİP 2 MONTAJ</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/2050</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Yağ sıyırıcı komple; arızada makine çalışır, banyo ömrü kısalır. Alt parçalar (motor, kontaktör, termik) ayrı stoklanır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>07 04649</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>YAĞ SIYIRICI KOMPLESİ TİP 3 MONTAJ</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>KBN 2B 1850</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Yağ sıyırıcı komple; arızada makine çalışır, banyo ömrü kısalır. Alt parçalar (motor, kontaktör, termik) ayrı stoklanır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>07 05519</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>OTOMATİK TANK BOŞALTMA (KBN 1B)</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Otomatik tank boşaltma; arızada boşaltma manuel yapılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>07 04925</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>OTOMATİK TANK BOŞALTMA (KBN 2B)</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>KBN 2B 1650/2050</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Otomatik tank boşaltma; arızada boşaltma manuel yapılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>07 09158</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>OTOMATİK TANK BOŞALTMA (KBN 2B 1850)</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>KBN 2B 1850</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>A+2+Z → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Otomatik tank boşaltma; arızada boşaltma manuel yapılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>07 00511</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>KBN DOZAJ ÜNİTESİ 1 BANYO İÇİN</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>A+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Kimyasal dozaj; arızada manuel dozaj ile çalışılabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>10 18815</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>DOZAJ POMPASI DOSATRON D25RE5 AF 2,5 M3/SAAT</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>photos/10 18815.jpg</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>KBN 1B 1850</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>A+2+O → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Kimyasal dozaj; arızada manuel dozaj ile çalışılabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>07 00551</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>KBN SIZINTI TAVASI UYARI SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>B+3+O → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Sızıntı tavası uyarı sistemi; arızada sızıntı fark edilmez, zemin/pano riski.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>10 04814</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>TEK TARAFLI P.VALF 24VDC 3V210-08-NC 1/4" 3-2</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>photos/10 04814.jpg</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>B+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>24 VDC pnömatik valf; arızada silindir hareket etmez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>10 07492</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>ÇİFT TARAFLI P.VALF 24VDC 4V220-08 1/4" 5-2</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>photos/10 07492.jpg</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>KBN 2B 1650/2050</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>B+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>24 VDC pnömatik valf; arızada silindir hareket etmez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>10 05243</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>PNÖMATİK SİLİNDİR SENSÖRÜ 39CMSE020 CS1E020 CS1-E</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>KBN 2B 1650/2050</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>B+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Pnömatik silindir konum sensörü CS1-E; arızada konum onayı alınmaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>10 16858</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>BASINÇ ŞALTERİ 1-12 BAR 1/4" DS1A3012</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>B+2+K → 1 adet · orta aşınma — 1 yedek</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Hava basınç şalteri 1–12 bar; arızada pnömatik onay alınmaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>10 03206</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>TEPE LAMBASI IK53F-024XEM03-24 FLAŞ 24V.2K.SABİT</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>photos/10 03206.jpg</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>KBN 1B 1650/1850 · KBN 2B 1650</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>A+3+K → 0 adet · seyrek arıza — listede tut, siparişle</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Sinyal / tepe lambası; arızada makine çalışır, uyarı görülmez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>10 01332</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K1610M7 220V</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K1610M7, 16 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>10 01331</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K0910M7 220V</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K0910M7, 9 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>10 02314</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>KONTAKTÖR LC1K0610M7 220V</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>photos/10 01331.jpg</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Pano</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>B+1+K → 2 adet · sık aşınma — depo seti</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Schneider TeSys K LC1K0610M7, 6 A, bobin 220 V AC; motor ve rezistans hattını anahtarlar. Kontaklar aşınır — LR2K termik röle ile birlikte kullanılır.</t>
         </is>
       </c>
     </row>

--- a/KRİTİK PARÇA LİSTESİ/Kritik-Parca-Listeleri.xlsx
+++ b/KRİTİK PARÇA LİSTESİ/Kritik-Parca-Listeleri.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,11 @@
           <t>PASLANMAZ SEVİYE BEKÇİSİ</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr"/>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>photos/10 00296.jpg</t>
+        </is>
+      </c>
       <c r="D509" t="inlineStr">
         <is>
           <t>LYM 950–1500</t>
@@ -7998,7 +8002,11 @@
           <t>REZİSTANS 220V 2000W 112CM SERP. DİKİŞSİZ AISI316</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>photos/10 07455.jpg</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr">
         <is>
           <t>VDL 2B 40/50/60/80</t>
@@ -8772,7 +8780,11 @@
           <t>EMİŞ FİLTRESİ KOMPLESİ (PYM2,KBN,VDL,ULT,KNV)</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>photos/07 00670.jpg</t>
+        </is>
+      </c>
       <c r="D521" t="inlineStr">
         <is>
           <t>VDL 1B 40 · VDL 2B 40/50/60/80</t>
@@ -12137,7 +12149,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850</t>
+          <t>KBN 1B 1650/1850/2050/2350</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -12358,10 +12370,14 @@
           <t>REZİSTANS KOMPLESİ 8000W 50CM DÜZ DİKİŞSİZ</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>photos/07 15142.jpg</t>
+        </is>
+      </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>KBN 2B 2050</t>
+          <t>KBN 2B 1650/1850/2050</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -13189,7 +13205,11 @@
           <t>POMPA HMSE 40-200/75</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>photos/10 17121.jpg</t>
+        </is>
+      </c>
       <c r="D521" t="inlineStr">
         <is>
           <t>KBN 1B 1650/1850</t>
@@ -13560,7 +13580,11 @@
           <t>EMİŞ FİLTRESİ KOMPLESİ (PYM2,KBN,VDL,ULT,KNV)</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr"/>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>photos/07 00670.jpg</t>
+        </is>
+      </c>
       <c r="D528" t="inlineStr">
         <is>
           <t>KBN 1B 1650/1850/2050/2350 · KBN 2B 1650/1850/2050</t>
@@ -14379,7 +14403,11 @@
           <t>PNÖMATİK SİLİNDİR SENSÖRÜ 39CMSE020 CS1E020 CS1-E</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr"/>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>photos/10 05243.jpg</t>
+        </is>
+      </c>
       <c r="D543" t="inlineStr">
         <is>
           <t>KBN 2B 1650/2050</t>
@@ -14432,7 +14460,11 @@
           <t>BASINÇ ŞALTERİ 1-12 BAR 1/4" DS1A3012</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr"/>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>photos/10 16858.jpg</t>
+        </is>
+      </c>
       <c r="D544" t="inlineStr">
         <is>
           <t>KBN 1B 1650 · KBN 2B 1650</t>
